--- a/data/trans_orig/P05A07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A07-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2012</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>425475</t>
+          <t>424391</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>477324</t>
+          <t>475202</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>410116</t>
+          <t>408080</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>461627</t>
+          <t>461745</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>851429</t>
+          <t>851705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>922827</t>
+          <t>924356</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,29%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189380</t>
+          <t>189971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238390</t>
+          <t>241468</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>189719</t>
+          <t>188004</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241112</t>
+          <t>241402</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>395745</t>
+          <t>395419</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>464969</t>
+          <t>463303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26692</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52575</t>
+          <t>50591</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32185</t>
+          <t>32101</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57124</t>
+          <t>56835</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63414</t>
+          <t>66139</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98686</t>
+          <t>98350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>535484</t>
+          <t>534250</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>597472</t>
+          <t>599556</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>542643</t>
+          <t>538917</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>607423</t>
+          <t>605917</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1092227</t>
+          <t>1093281</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1187512</t>
+          <t>1186264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>58,16%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>329593</t>
+          <t>327889</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>392891</t>
+          <t>393281</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>317831</t>
+          <t>318932</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>380639</t>
+          <t>382690</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>666309</t>
+          <t>666796</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>752500</t>
+          <t>757301</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68171</t>
+          <t>67561</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108846</t>
+          <t>105025</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>84153</t>
+          <t>83965</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125678</t>
+          <t>125104</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164095</t>
+          <t>163287</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>217733</t>
+          <t>221656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>363304</t>
+          <t>364496</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>423128</t>
+          <t>424125</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>378660</t>
+          <t>381462</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>442236</t>
+          <t>438144</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>762430</t>
+          <t>762414</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>844603</t>
+          <t>845535</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,24%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>227231</t>
+          <t>222640</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>281414</t>
+          <t>281390</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218860</t>
+          <t>218754</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>273775</t>
+          <t>272530</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>460264</t>
+          <t>460565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>539635</t>
+          <t>538868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93274</t>
+          <t>90505</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133816</t>
+          <t>132440</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98464</t>
+          <t>98621</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140774</t>
+          <t>138692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199248</t>
+          <t>199695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>258119</t>
+          <t>257453</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>352323</t>
+          <t>352772</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>418086</t>
+          <t>417512</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>388967</t>
+          <t>387567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>451727</t>
+          <t>453941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>762567</t>
+          <t>758199</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>848687</t>
+          <t>849029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>332267</t>
+          <t>335304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>397064</t>
+          <t>393431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>377522</t>
+          <t>377707</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>442968</t>
+          <t>439654</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>729486</t>
+          <t>727056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>820996</t>
+          <t>815881</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,86%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171204</t>
+          <t>171716</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>223175</t>
+          <t>224560</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>194609</t>
+          <t>192948</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>247867</t>
+          <t>247431</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>379429</t>
+          <t>380086</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>457116</t>
+          <t>452931</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,68%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1743116</t>
+          <t>1729135</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1858701</t>
+          <t>1849140</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1778080</t>
+          <t>1780728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1901421</t>
+          <t>1899873</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3552114</t>
+          <t>3552897</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3721761</t>
+          <t>3722514</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1133805</t>
+          <t>1132119</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1245132</t>
+          <t>1247293</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1159305</t>
+          <t>1157912</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1278472</t>
+          <t>1273602</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2330850</t>
+          <t>2328104</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2489938</t>
+          <t>2487926</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>392611</t>
+          <t>394468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>476508</t>
+          <t>472340</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>443808</t>
+          <t>447356</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>528677</t>
+          <t>530518</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>861559</t>
+          <t>862966</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>978613</t>
+          <t>976599</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2016</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2016 (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>538398</t>
+          <t>540836</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>578038</t>
+          <t>580024</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>536483</t>
+          <t>534468</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>575151</t>
+          <t>572592</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1089267</t>
+          <t>1086225</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1143896</t>
+          <t>1142688</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,27%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75165</t>
+          <t>73952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109277</t>
+          <t>111134</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65821</t>
+          <t>65777</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98537</t>
+          <t>97920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148738</t>
+          <t>149649</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196296</t>
+          <t>200618</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,97%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11790</t>
+          <t>11226</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30542</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>21900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44085</t>
+          <t>43693</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38949</t>
+          <t>38840</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>69800</t>
+          <t>67953</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>665903</t>
+          <t>665162</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>729595</t>
+          <t>725851</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>696310</t>
+          <t>694036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>758298</t>
+          <t>755921</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1381002</t>
+          <t>1381428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1466169</t>
+          <t>1463726</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,39%</t>
+          <t>71,28%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>227276</t>
+          <t>227801</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>284080</t>
+          <t>284008</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>213111</t>
+          <t>212972</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>268410</t>
+          <t>268418</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>455482</t>
+          <t>454953</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>533764</t>
+          <t>535447</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50181</t>
+          <t>50268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82843</t>
+          <t>82910</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55264</t>
+          <t>54964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88323</t>
+          <t>87044</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114866</t>
+          <t>114463</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159497</t>
+          <t>160196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>425400</t>
+          <t>421945</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>480684</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>439918</t>
+          <t>439388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>491565</t>
+          <t>494123</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>876374</t>
+          <t>875909</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>953102</t>
+          <t>955237</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,94%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,06%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193771</t>
+          <t>194114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>245447</t>
+          <t>244616</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178412</t>
+          <t>179690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>230334</t>
+          <t>228714</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>390359</t>
+          <t>388520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>459007</t>
+          <t>461050</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68681</t>
+          <t>67404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104595</t>
+          <t>104136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91120</t>
+          <t>92648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>133321</t>
+          <t>132871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169546</t>
+          <t>172634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224980</t>
+          <t>226408</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,71%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>469728</t>
+          <t>469721</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>531815</t>
+          <t>530219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>526428</t>
+          <t>526279</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>591792</t>
+          <t>591763</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1018373</t>
+          <t>1019407</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1103006</t>
+          <t>1110036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>238820</t>
+          <t>242622</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>296867</t>
+          <t>296506</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>249719</t>
+          <t>252004</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>310427</t>
+          <t>310117</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>508131</t>
+          <t>505363</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>586312</t>
+          <t>589779</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140943</t>
+          <t>142544</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>189731</t>
+          <t>190763</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>171801</t>
+          <t>175240</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>224247</t>
+          <t>226161</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>326448</t>
+          <t>328011</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>400902</t>
+          <t>397811</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2151544</t>
+          <t>2159371</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2265633</t>
+          <t>2269493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2249527</t>
+          <t>2252318</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2360649</t>
+          <t>2362044</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4437544</t>
+          <t>4441809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4592643</t>
+          <t>4598625</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>783868</t>
+          <t>779793</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>884938</t>
+          <t>883661</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>759569</t>
+          <t>756270</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>856330</t>
+          <t>862783</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1573943</t>
+          <t>1569334</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1711338</t>
+          <t>1719785</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>303063</t>
+          <t>302388</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>372463</t>
+          <t>370654</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>371894</t>
+          <t>374471</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>453696</t>
+          <t>450897</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>689472</t>
+          <t>697281</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>799951</t>
+          <t>804012</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -5561,7 +5561,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2023</t>
+          <t>Población según si en el barrio donde vive hay trafico intenso de vehículos de motor en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>548470</t>
+          <t>548868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>580284</t>
+          <t>581954</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>642344</t>
+          <t>642371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>673712</t>
+          <t>673234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1201094</t>
+          <t>1201039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1247687</t>
+          <t>1246202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,65%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34849</t>
+          <t>34731</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61457</t>
+          <t>62245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33615</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57080</t>
+          <t>56748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75896</t>
+          <t>75040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110301</t>
+          <t>110851</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>13310</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33100</t>
+          <t>34032</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5997,12 +5997,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15812</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33894</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6032,12 +6032,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>32024</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>59943</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>959535</t>
+          <t>956760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1102940</t>
+          <t>1099007</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>726886</t>
+          <t>722266</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>770907</t>
+          <t>769388</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1704945</t>
+          <t>1702168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1900740</t>
+          <t>1889922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>59616</t>
+          <t>62948</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>158006</t>
+          <t>160764</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116074</t>
+          <t>118080</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>152930</t>
+          <t>156577</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>175483</t>
+          <t>170831</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>296195</t>
+          <t>298255</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30716</t>
+          <t>29762</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79811</t>
+          <t>82200</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60364</t>
+          <t>60963</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89669</t>
+          <t>91406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81970</t>
+          <t>90315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160098</t>
+          <t>159849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>500177</t>
+          <t>499609</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>551539</t>
+          <t>549412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,92%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>707444</t>
+          <t>706773</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>850446</t>
+          <t>856368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1225522</t>
+          <t>1230556</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1402939</t>
+          <t>1409320</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107361</t>
+          <t>107495</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151299</t>
+          <t>151311</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51699</t>
+          <t>51654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148729</t>
+          <t>150825</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>162434</t>
+          <t>159454</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>289345</t>
+          <t>286220</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37752</t>
+          <t>36758</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69498</t>
+          <t>69345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27507</t>
+          <t>27543</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80855</t>
+          <t>82369</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71738</t>
+          <t>71143</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136134</t>
+          <t>133527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>473934</t>
+          <t>474224</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>540457</t>
+          <t>541904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602466</t>
+          <t>599146</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>736904</t>
+          <t>734013</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1096973</t>
+          <t>1096594</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1259020</t>
+          <t>1250844</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>61,91%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>226683</t>
+          <t>226146</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>286096</t>
+          <t>283422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>210148</t>
+          <t>206307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>291579</t>
+          <t>292804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>449900</t>
+          <t>448796</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>560342</t>
+          <t>558549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,65%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>139789</t>
+          <t>140904</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>193734</t>
+          <t>191705</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>151307</t>
+          <t>148639</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>214177</t>
+          <t>213399</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>306254</t>
+          <t>310095</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387658</t>
+          <t>390957</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,35%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2530324</t>
+          <t>2525983</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2834062</t>
+          <t>2794662</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2735857</t>
+          <t>2738428</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2982235</t>
+          <t>2968838</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5299365</t>
+          <t>5297229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5651024</t>
+          <t>5674132</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,16%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>425937</t>
+          <t>434912</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>608139</t>
+          <t>616424</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,47 +7708,47 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
+          <t>12,58%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>17,83%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>551521</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>457222</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>608826</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>12,32%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>858</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>551521</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>451294</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>609064</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>962630</t>
+          <t>945318</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1195153</t>
+          <t>1198308</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228693</t>
+          <t>225212</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>340665</t>
+          <t>337701</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>275689</t>
+          <t>278067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>383117</t>
+          <t>381928</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>552304</t>
+          <t>550355</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>705616</t>
+          <t>698791</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P05A07-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P05A07-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>424391</t>
+          <t>424174</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>475202</t>
+          <t>476945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>408080</t>
+          <t>409517</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>461745</t>
+          <t>461319</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>851705</t>
+          <t>851622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>924356</t>
+          <t>925131</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,35%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>189971</t>
+          <t>187771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>241468</t>
+          <t>237431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>188004</t>
+          <t>189523</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>241402</t>
+          <t>239955</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>395419</t>
+          <t>395877</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>463303</t>
+          <t>461353</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>26223</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50591</t>
+          <t>51247</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>32101</t>
+          <t>31262</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56835</t>
+          <t>57800</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>66139</t>
+          <t>64923</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>98350</t>
+          <t>101150</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>534250</t>
+          <t>531264</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>599556</t>
+          <t>599962</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>59,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>538917</t>
+          <t>540532</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>605917</t>
+          <t>607067</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1093281</t>
+          <t>1099331</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1186264</t>
+          <t>1187576</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,23%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>327889</t>
+          <t>329282</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>393281</t>
+          <t>392567</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>318932</t>
+          <t>317861</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382690</t>
+          <t>382807</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>666796</t>
+          <t>663208</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>757301</t>
+          <t>754766</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67561</t>
+          <t>67608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105025</t>
+          <t>106034</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>83965</t>
+          <t>83135</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125104</t>
+          <t>125618</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>163287</t>
+          <t>164538</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>221656</t>
+          <t>222835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>364496</t>
+          <t>366259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>424125</t>
+          <t>422655</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>381462</t>
+          <t>381990</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>438144</t>
+          <t>440054</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>762414</t>
+          <t>761793</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>845535</t>
+          <t>841084</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>222640</t>
+          <t>226077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>281390</t>
+          <t>278960</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218754</t>
+          <t>218376</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>272530</t>
+          <t>272648</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>460565</t>
+          <t>464200</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>538868</t>
+          <t>539326</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,23%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90505</t>
+          <t>92841</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>132440</t>
+          <t>131865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98621</t>
+          <t>96090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>138692</t>
+          <t>136440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199695</t>
+          <t>202446</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>257453</t>
+          <t>260385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>352772</t>
+          <t>354402</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>417512</t>
+          <t>413812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>387567</t>
+          <t>388668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>453941</t>
+          <t>452891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>758199</t>
+          <t>760976</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>849029</t>
+          <t>850455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,59%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>335304</t>
+          <t>333194</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>393431</t>
+          <t>395386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>377707</t>
+          <t>379175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439654</t>
+          <t>441616</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>727056</t>
+          <t>729645</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>815881</t>
+          <t>815552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,84%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171716</t>
+          <t>174295</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>224560</t>
+          <t>223186</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>192948</t>
+          <t>194067</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>247431</t>
+          <t>251296</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>380086</t>
+          <t>381651</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>452931</t>
+          <t>455887</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1729135</t>
+          <t>1738050</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1849140</t>
+          <t>1854928</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1780728</t>
+          <t>1772456</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1899873</t>
+          <t>1896145</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,26%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3552897</t>
+          <t>3548327</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3722514</t>
+          <t>3729371</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,57%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1132119</t>
+          <t>1137479</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1247293</t>
+          <t>1249172</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1157912</t>
+          <t>1165054</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1273602</t>
+          <t>1284296</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>2328104</t>
+          <t>2326407</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2487926</t>
+          <t>2489037</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>394468</t>
+          <t>395748</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>472340</t>
+          <t>473596</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>447356</t>
+          <t>442789</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>530518</t>
+          <t>529264</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>862966</t>
+          <t>856591</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>976599</t>
+          <t>976967</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>540836</t>
+          <t>540341</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>580024</t>
+          <t>579367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>534468</t>
+          <t>535941</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>572592</t>
+          <t>572789</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1086225</t>
+          <t>1088504</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1142688</t>
+          <t>1143712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73952</t>
+          <t>74163</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111134</t>
+          <t>110372</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>65777</t>
+          <t>65814</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97920</t>
+          <t>98900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149649</t>
+          <t>149770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200618</t>
+          <t>198480</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11226</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30084</t>
+          <t>29763</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21900</t>
+          <t>22506</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43693</t>
+          <t>43283</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>38840</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67953</t>
+          <t>68154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>665162</t>
+          <t>665838</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>725851</t>
+          <t>728255</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>694036</t>
+          <t>694001</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>755921</t>
+          <t>754673</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1381428</t>
+          <t>1380580</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1463726</t>
+          <t>1464573</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>71,32%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>227801</t>
+          <t>225406</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>284008</t>
+          <t>284531</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>212972</t>
+          <t>212372</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>268418</t>
+          <t>268042</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>454953</t>
+          <t>456386</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>535447</t>
+          <t>536763</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50268</t>
+          <t>50007</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82910</t>
+          <t>83576</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54964</t>
+          <t>54632</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87044</t>
+          <t>87428</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114463</t>
+          <t>114826</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160196</t>
+          <t>159894</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>421945</t>
+          <t>423606</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>479234</t>
+          <t>479623</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>439388</t>
+          <t>438521</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>494123</t>
+          <t>494287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>875909</t>
+          <t>879175</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>955237</t>
+          <t>956568</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>62,06%</t>
+          <t>62,15%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194114</t>
+          <t>196003</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>244616</t>
+          <t>246084</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>179690</t>
+          <t>178368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>228714</t>
+          <t>228524</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>388520</t>
+          <t>389612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>461050</t>
+          <t>459688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67404</t>
+          <t>69192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104136</t>
+          <t>104850</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>92648</t>
+          <t>94323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132871</t>
+          <t>133998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>172634</t>
+          <t>171543</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>226408</t>
+          <t>224377</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>469721</t>
+          <t>469991</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>530219</t>
+          <t>531646</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>526279</t>
+          <t>524291</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>591763</t>
+          <t>593018</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1019407</t>
+          <t>1010920</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1110036</t>
+          <t>1102460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,9%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>242622</t>
+          <t>240337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>296506</t>
+          <t>295350</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>252004</t>
+          <t>253876</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>310117</t>
+          <t>313007</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>505363</t>
+          <t>511671</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>589779</t>
+          <t>590669</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>142544</t>
+          <t>142552</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>190763</t>
+          <t>188938</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>175240</t>
+          <t>173679</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>226161</t>
+          <t>226410</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>328011</t>
+          <t>329332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>397811</t>
+          <t>401168</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2159371</t>
+          <t>2147596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2269493</t>
+          <t>2263126</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2252318</t>
+          <t>2251117</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2362044</t>
+          <t>2362695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4441809</t>
+          <t>4436786</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4598625</t>
+          <t>4601005</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>779793</t>
+          <t>788597</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>883661</t>
+          <t>886888</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>756270</t>
+          <t>757766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>862783</t>
+          <t>856451</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1569334</t>
+          <t>1567552</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1719785</t>
+          <t>1718443</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>302388</t>
+          <t>302935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>370654</t>
+          <t>373656</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>374471</t>
+          <t>374366</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>450897</t>
+          <t>455926</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>697281</t>
+          <t>693249</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>804012</t>
+          <t>800437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,59%</t>
         </is>
       </c>
     </row>
@@ -5751,32 +5751,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>566630</t>
+          <t>616616</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>548868</t>
+          <t>596844</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>581954</t>
+          <t>632171</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5786,32 +5786,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>658099</t>
+          <t>661453</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>642371</t>
+          <t>646616</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>673234</t>
+          <t>673857</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5821,32 +5821,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1224729</t>
+          <t>1278068</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1201039</t>
+          <t>1256322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1246202</t>
+          <t>1299847</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -5864,32 +5864,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46696</t>
+          <t>49989</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34731</t>
+          <t>37485</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62245</t>
+          <t>65409</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5899,32 +5899,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44684</t>
+          <t>48486</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33504</t>
+          <t>38689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56748</t>
+          <t>61876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>91379</t>
+          <t>98475</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>75040</t>
+          <t>80802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110851</t>
+          <t>115115</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -5977,32 +5977,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>21096</t>
+          <t>23020</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13310</t>
+          <t>14664</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34032</t>
+          <t>37040</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6012,32 +6012,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22547</t>
+          <t>24241</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15628</t>
+          <t>17178</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32265</t>
+          <t>34449</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6047,32 +6047,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>43644</t>
+          <t>47261</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32024</t>
+          <t>35645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58807</t>
+          <t>64176</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6090,17 +6090,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>634422</t>
+          <t>689624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6125,17 +6125,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1359752</t>
+          <t>1423804</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1359752</t>
+          <t>1423804</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1359752</t>
+          <t>1423804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6207,32 +6207,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1015698</t>
+          <t>848425</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>956760</t>
+          <t>817172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1099007</t>
+          <t>875566</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6242,32 +6242,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>749670</t>
+          <t>840681</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>722266</t>
+          <t>816924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>769388</t>
+          <t>867576</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6277,32 +6277,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1765368</t>
+          <t>1689106</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1702168</t>
+          <t>1649692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1889922</t>
+          <t>1728221</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6320,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118823</t>
+          <t>134734</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62948</t>
+          <t>112718</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160764</t>
+          <t>162451</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6355,32 +6355,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>134555</t>
+          <t>148508</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118080</t>
+          <t>129929</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156577</t>
+          <t>172307</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6390,32 +6390,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>253377</t>
+          <t>283242</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>170831</t>
+          <t>253100</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>298255</t>
+          <t>320346</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -6433,32 +6433,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>57805</t>
+          <t>65204</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29762</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>82200</t>
+          <t>82004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6468,32 +6468,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>73815</t>
+          <t>81600</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60963</t>
+          <t>65366</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91406</t>
+          <t>98820</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6503,32 +6503,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>131620</t>
+          <t>146804</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90315</t>
+          <t>124083</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159849</t>
+          <t>171030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -6546,17 +6546,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192326</t>
+          <t>1048364</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192326</t>
+          <t>1048364</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192326</t>
+          <t>1048364</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6581,17 +6581,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>958039</t>
+          <t>1070789</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>958039</t>
+          <t>1070789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>958039</t>
+          <t>1070789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2150365</t>
+          <t>2119153</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2150365</t>
+          <t>2119153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2150365</t>
+          <t>2119153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6663,32 +6663,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>525584</t>
+          <t>585674</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>499609</t>
+          <t>553667</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>549412</t>
+          <t>609821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6698,32 +6698,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>765764</t>
+          <t>611091</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>706773</t>
+          <t>587663</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>856368</t>
+          <t>634471</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6733,32 +6733,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1291348</t>
+          <t>1196765</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1230556</t>
+          <t>1159209</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1409320</t>
+          <t>1230591</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>76,38%</t>
         </is>
       </c>
     </row>
@@ -6776,32 +6776,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>128100</t>
+          <t>151843</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107495</t>
+          <t>129541</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151311</t>
+          <t>178804</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6811,32 +6811,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>110033</t>
+          <t>131827</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>111647</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>150825</t>
+          <t>152414</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6846,32 +6846,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>238133</t>
+          <t>283670</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159454</t>
+          <t>252556</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>286220</t>
+          <t>317330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -6889,32 +6889,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>50832</t>
+          <t>64379</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36758</t>
+          <t>47735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>69345</t>
+          <t>82769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6924,32 +6924,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>57245</t>
+          <t>66229</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27543</t>
+          <t>53202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>82369</t>
+          <t>83544</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6959,32 +6959,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>108077</t>
+          <t>130608</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71143</t>
+          <t>110008</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>133527</t>
+          <t>155325</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -7002,17 +7002,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7037,17 +7037,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933042</t>
+          <t>809147</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>933042</t>
+          <t>809147</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933042</t>
+          <t>809147</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1637558</t>
+          <t>1611043</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1637558</t>
+          <t>1611043</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1637558</t>
+          <t>1611043</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>507503</t>
+          <t>538614</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>474224</t>
+          <t>502628</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>541904</t>
+          <t>571825</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>642998</t>
+          <t>610571</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>599146</t>
+          <t>578921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>734013</t>
+          <t>636608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1150502</t>
+          <t>1149186</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1096594</t>
+          <t>1103596</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1250844</t>
+          <t>1192441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -7232,32 +7232,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>254558</t>
+          <t>276391</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>226146</t>
+          <t>245920</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>283422</t>
+          <t>305831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7267,32 +7267,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>262250</t>
+          <t>292712</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>206307</t>
+          <t>268416</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>292804</t>
+          <t>319186</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>516808</t>
+          <t>569103</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>448796</t>
+          <t>527932</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>558549</t>
+          <t>609081</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>28,91%</t>
         </is>
       </c>
     </row>
@@ -7345,32 +7345,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>164606</t>
+          <t>173939</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140904</t>
+          <t>150061</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>191705</t>
+          <t>202207</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7380,32 +7380,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>188424</t>
+          <t>214420</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>148639</t>
+          <t>192203</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>213399</t>
+          <t>240841</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7415,32 +7415,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>353029</t>
+          <t>388358</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>310095</t>
+          <t>353151</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>390957</t>
+          <t>422823</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -7458,17 +7458,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>926667</t>
+          <t>988944</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7493,17 +7493,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1093672</t>
+          <t>1117703</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1093672</t>
+          <t>1117703</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1093672</t>
+          <t>1117703</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7528,17 +7528,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2020339</t>
+          <t>2106647</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2020339</t>
+          <t>2106647</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2020339</t>
+          <t>2106647</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2615415</t>
+          <t>2589330</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2525983</t>
+          <t>2536045</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2794662</t>
+          <t>2650710</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7610,32 +7610,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2816531</t>
+          <t>2723796</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2738428</t>
+          <t>2672448</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2968838</t>
+          <t>2773821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>5431947</t>
+          <t>5313125</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5297229</t>
+          <t>5235967</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5674132</t>
+          <t>5390941</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>75,78%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -7688,32 +7688,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>548176</t>
+          <t>612957</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>434912</t>
+          <t>568661</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>616424</t>
+          <t>662512</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7723,32 +7723,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>551521</t>
+          <t>621533</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>457222</t>
+          <t>580140</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608826</t>
+          <t>661974</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7758,32 +7758,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1099697</t>
+          <t>1234490</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>945318</t>
+          <t>1171461</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1198308</t>
+          <t>1293907</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -7801,32 +7801,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>294339</t>
+          <t>326541</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>225212</t>
+          <t>293368</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>337701</t>
+          <t>371754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7836,32 +7836,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>342031</t>
+          <t>386490</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>278067</t>
+          <t>352469</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>381928</t>
+          <t>425390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>636370</t>
+          <t>713031</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>550355</t>
+          <t>660668</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>698791</t>
+          <t>764531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -7914,17 +7914,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3457930</t>
+          <t>3528828</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3457930</t>
+          <t>3528828</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3457930</t>
+          <t>3528828</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7949,17 +7949,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3710083</t>
+          <t>3731819</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3710083</t>
+          <t>3731819</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3710083</t>
+          <t>3731819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7168014</t>
+          <t>7260646</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7168014</t>
+          <t>7260646</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7168014</t>
+          <t>7260646</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
